--- a/app/ejemplos/DEXIAE_ejemplo_extracto.xlsx
+++ b/app/ejemplos/DEXIAE_ejemplo_extracto.xlsx
@@ -8207,7 +8207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/09/2026 00:35</t>
+          <t>01/10/2026 11:46</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.7.5</t>
+          <t>2.8.0</t>
         </is>
       </c>
     </row>
